--- a/stories/arbres/ATOM-SOC.MET.001-07.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hortense marche avec maman. Un bus s'arrête. Le chauffeur ouvre la porte. Maman dit : c'est un métier. Hortense dit : chauffeur. Le chauffeur fait un geste utile. Il conduit. Ensuite, le marché. Ça sent le pain chaud. Le boulanger pose les baguettes. Maman dit : c'est un métier. Hortense dit : boulanger. Le boulanger fait un geste utile. Il prépare le pain. Ils passent chez le médecin. Le médecin écoute le cœur. Papa les rejoint. Papa dit : c'est un métier. Hortense dit : médecin. Le médecin fait un geste utile. Il soigne. Après, ils voient l'école. La maîtresse range des livres. Maman dit : c'est un métier. Hortense dit : maîtresse. La maîtresse fait un geste utile. Elle aide les enfants. Chaque métier a un geste utile.</t>
+          <t>Hortense marche avec maman. Un bus s'arrête. Le chauffeur ouvre la porte. C'est un métier. Chauffeur. Le chauffeur fait un geste utile. Il conduit. Ensuite, le marché. Ça sent le pain chaud. Le boulanger pose les baguettes. C'est un métier. Boulanger. Le boulanger fait un geste utile. Il prépare le pain. Ils passent chez le médecin. Le médecin écoute le cœur. Papa les rejoint. C'est un métier. Médecin. Le médecin fait un geste utile. Il soigne. Après, ils voient l'école. La maîtresse range des livres. C'est un métier. Maîtresse. La maîtresse fait un geste utile. Elle aide les enfants. Chaque métier a un geste utile.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,23 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hortense marche avec maman. Un bus s'arrête. Le chauffeur ouvre la porte.
+maman|C'est un métier.
+enfant-f|Chauffeur.
+narrateur|Le chauffeur fait un geste utile. Il conduit. Ensuite, le marché. Ça sent le pain chaud. Le boulanger pose les baguettes.
+maman|C'est un métier.
+enfant-f|Boulanger.
+narrateur|Le boulanger fait un geste utile. Il prépare le pain. Ils passent chez le médecin. Le médecin écoute le cœur. Papa les rejoint.
+papa|C'est un métier.
+enfant-f|Médecin.
+narrateur|Le médecin fait un geste utile. Il soigne. Après, ils voient l'école. La maîtresse range des livres.
+maman|C'est un métier.
+enfant-f|Maîtresse.
+narrateur|La maîtresse fait un geste utile. Elle aide les enfants. Chaque métier a un geste utile.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le boulanger pose le pain. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hortense a nommé les métiers. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1838,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hortense serre la main de maman. Ils rentrent à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2005,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2045,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.MET.001-07.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1322,6 +1327,7 @@
 narrateur|La maîtresse fait un geste utile. Elle aide les enfants. Chaque métier a un geste utile.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1511,7 @@
           <t>narrateur|Le boulanger pose le pain. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Hortense a nommé les métiers. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1843,6 +1851,7 @@
           <t>narrateur|Hortense serre la main de maman. Ils rentrent à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2010,6 +2019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2028,7 +2038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2052,6 +2062,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2253,6 +2277,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.MET.001-07.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hortense nomme les métiers du quartier</t>
+          <t>La clochette et la rose</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorina veut un livre de fleurs, puis une vraie rose. Le livre est trop haut. La libraire le glisse. Chez la fleuriste, une goutte vise la couverture. Livre au sec, rose dans le verre.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hortense marche avec maman. Un bus s'arrête. Le chauffeur ouvre la porte. C'est un métier. Chauffeur. Le chauffeur fait un geste utile. Il conduit. Ensuite, le marché. Ça sent le pain chaud. Le boulanger pose les baguettes. C'est un métier. Boulanger. Le boulanger fait un geste utile. Il prépare le pain. Ils passent chez le médecin. Le médecin écoute le cœur. Papa les rejoint. C'est un métier. Médecin. Le médecin fait un geste utile. Il soigne. Après, ils voient l'école. La maîtresse range des livres. C'est un métier. Maîtresse. La maîtresse fait un geste utile. Elle aide les enfants. Chaque métier a un geste utile.</t>
+          <t>La clochette de la librairie tinte deux fois. Les pages sentent le papier neuf et la colle. Un rayon penche, trop haut pour une main d'enfant. Victorina vit dans ce quartier, avec maman et papa. Dehors, un platane jette des ombres rondes. Je veux un livre, maman. Un livre avec des fleurs. On demande à la libraire ? Elle est derrière le comptoir. En ce moment, Victorina suit le dos des livres. Le dos est lisse, un peu froid. Le livre aux fleurs est trop haut. Je ne l'ai pas. On reste en bas. On appelle. La libraire peut le prendre. La libraire avance, lunettes sur le nez. Elle glisse le livre, tout doux, vers les mains de Victorina. Merci. C'est la libraire. C'est son métier. Elle range les livres. Elle les trouve, aussi. Victorina ouvre une page. Une rose y est dessinée, trop plate. Je veux une vraie. Chez la fleuriste, alors. Juste après la librairie. La clochette tinte encore, en partant. Le livre tape un peu la hanche. Tu le tiens ? Oui, papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hortense marche avec maman. Un bus s'arrête. Le chauffeur ouvre la porte. Maman dit : c'est un &lt;emphasis level="moderate"&gt;métier&lt;/emphasis&gt;. Hortense dit : chauffeur. Le chauffeur fait un geste utile. Il conduit. Ensuite, le marché. Ça sent le pain chaud. Le boulanger pose les baguettes. Maman dit : c'est un métier. Hortense dit : boulanger. Le boulanger fait un geste utile. Il prépare le pain. Ils passent chez le médecin. Le médecin écoute le cœur. Papa les rejoint. Papa dit : c'est un métier. Hortense dit : médecin. Le médecin fait un geste utile. Il soigne. Après, ils voient l'école. La maîtresse range des livres. Maman dit : c'est un métier. Hortense dit : maîtresse. La maîtresse fait un geste utile. Elle aide les enfants. Chaque métier a un geste utile.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La clochette de la librairie tinte deux fois. Les pages sentent le papier neuf et la colle. Un rayon penche, trop haut pour une main d'enfant. Victorina vit dans ce quartier, avec maman et papa. Dehors, un platane jette des ombres rondes. Je veux un livre, maman. Un livre avec des fleurs. On demande à la libraire ? Elle est derrière le comptoir. En ce moment, Victorina suit le dos des livres. Le dos est lisse, un peu froid. Le livre aux fleurs est trop haut. Je ne l'ai pas. On reste en bas. On appelle. La libraire peut le prendre. La libraire avance, lunettes sur le nez. Elle glisse le livre, tout doux, vers les mains de Victorina. Merci. C'est la libraire. C'est son métier. Elle range les livres. Elle les trouve, aussi. Victorina ouvre une page. Une rose y est dessinée, trop plate. Je veux une vraie. Chez la fleuriste, alors. Juste après la librairie. La clochette tinte encore, en partant. Le livre tape un peu la hanche. Tu le tiens ? Oui, papa.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,22 +1324,40 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hortense marche avec maman. Un bus s'arrête. Le chauffeur ouvre la porte.
-maman|C'est un métier.
-enfant-f|Chauffeur.
-narrateur|Le chauffeur fait un geste utile. Il conduit. Ensuite, le marché. Ça sent le pain chaud. Le boulanger pose les baguettes.
-maman|C'est un métier.
-enfant-f|Boulanger.
-narrateur|Le boulanger fait un geste utile. Il prépare le pain. Ils passent chez le médecin. Le médecin écoute le cœur. Papa les rejoint.
-papa|C'est un métier.
-enfant-f|Médecin.
-narrateur|Le médecin fait un geste utile. Il soigne. Après, ils voient l'école. La maîtresse range des livres.
-maman|C'est un métier.
-enfant-f|Maîtresse.
-narrateur|La maîtresse fait un geste utile. Elle aide les enfants. Chaque métier a un geste utile.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La clochette de la librairie tinte deux fois.
+narrateur|Les pages sentent le papier neuf et la colle.
+narrateur|Un rayon penche, trop haut pour une main d'enfant.
+narrateur|Victorina vit dans ce quartier, avec maman et papa.
+narrateur|Dehors, un platane jette des ombres rondes.
+enfant-f|Je veux un livre, maman.
+enfant-f|Un livre avec des fleurs.
+maman|On demande à la libraire ?
+papa|Elle est derrière le comptoir.
+narrateur|En ce moment, Victorina suit le dos des livres.
+narrateur|Le dos est lisse, un peu froid.
+narrateur|Le livre aux fleurs est trop haut.
+enfant-f|Je ne l'ai pas.
+maman|On reste en bas.
+maman|On appelle.
+papa|La libraire peut le prendre.
+narrateur|La libraire avance, lunettes sur le nez.
+narrateur|Elle glisse le livre, tout doux, vers les mains de Victorina.
+enfant-f|Merci.
+maman|C'est la libraire.
+maman|C'est son métier.
+enfant-f|Elle range les livres.
+papa|Elle les trouve, aussi.
+narrateur|Victorina ouvre une page.
+narrateur|Une rose y est dessinée, trop plate.
+enfant-f|Je veux une vraie.
+papa|Chez la fleuriste, alors.
+maman|Juste après la librairie.
+narrateur|La clochette tinte encore, en partant.
+narrateur|Le livre tape un peu la hanche.
+papa|Tu le tiens ?
+enfant-f|Oui, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1352,12 +1382,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le boulanger pose le pain. C'est quoi ?</t>
+          <t>La libraire range les livres. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le boulanger pose le pain. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La libraire range les livres. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1367,12 +1397,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>un métier</t>
+          <t>métier</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>un métier | métier | boulanger | le boulanger</t>
+          <t>métier | un métier | son métier | le métier | c'est un métier</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1387,7 +1417,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il fait un geste utile. C'est quoi ?</t>
+          <t>Elle trouve les livres. C'est quoi ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1436,7 +1466,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1508,10 +1538,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le boulanger pose le pain. C'est quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La libraire range les livres.
+narrateur|C'est quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,12 +1566,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hortense a nommé les métiers. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.</t>
+          <t>Le seau de la fleuriste est plein d'eau claire. Ça sent la rose et la tige coupée. Une goutte court sur le zinc. La fleuriste ! Oui. Elle aussi a un métier. Elle choisit les fleurs. Pour moi, une rose. Victorina pose le livre trop près du seau. Une goutte vise la couverture. Le livre ici, le seau là. Pardon. Elle recule le livre, tout de suite. La fleuriste tend une rose courte, encore fraîche. Merci. Merci. Bravo, Victorina. Tu as gardé le livre au sec. La rose sent plus fort que la page. Victorina a les deux, papier et pétale. On rentre ? Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hortense a nommé les &lt;emphasis level="moderate"&gt;métier&lt;/emphasis&gt;s. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le seau de la fleuriste est plein d'eau claire. Ça sent la rose et la tige coupée. Une goutte court sur le zinc. La fleuriste ! Oui. Elle aussi a un métier. Elle choisit les fleurs. Pour moi, une rose. Victorina pose le livre trop près du seau. Une goutte vise la couverture. Le livre ici, le seau là. Pardon. Elle recule le livre, tout de suite. La fleuriste tend une rose courte, encore fraîche. Merci. Merci. Bravo, Victorina. Tu as gardé le livre au sec. La rose sent plus fort que la page. Victorina a les deux, papier et pétale. On rentre ? Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1604,7 +1634,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1680,10 +1710,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hortense a nommé les métiers. Chauffeur. Boulanger. Médecin. Maîtresse. Chaque geste est utile.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le seau de la fleuriste est plein d'eau claire.
+narrateur|Ça sent la rose et la tige coupée.
+narrateur|Une goutte court sur le zinc.
+enfant-f|La fleuriste !
+maman|Oui.
+maman|Elle aussi a un métier.
+papa|Elle choisit les fleurs.
+enfant-f|Pour moi, une rose.
+narrateur|Victorina pose le livre trop près du seau.
+narrateur|Une goutte vise la couverture.
+papa|Le livre ici, le seau là.
+enfant-f|Pardon.
+narrateur|Elle recule le livre, tout de suite.
+narrateur|La fleuriste tend une rose courte, encore fraîche.
+maman|Merci.
+enfant-f|Merci.
+papa|Bravo, Victorina.
+papa|Tu as gardé le livre au sec.
+narrateur|La rose sent plus fort que la page.
+narrateur|Victorina a les deux, papier et pétale.
+maman|On rentre ?
+enfant-f|Oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,12 +1758,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hortense serre la main de maman. Ils rentrent à la maison.</t>
+          <t>Le platane fait encore des ronds sur le trottoir. Papa ouvre la porte de la maison. Maman cherche un verre d'eau, pour la rose. Le livre, sur la table. Et la rose, dans le verre. Les deux métiers t'ont aidée. La libraire, puis la fleuriste. Le livre, et la vraie. Tu veux que je tourne une page ? Celle de la rose. La page et la tige se regardent, un peu. Une goutte glisse dans le verre, sans bruit. Merci d'avoir reculé le livre. Il est resté sec.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hortense serre la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman. Ils rentrent à la maison.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le platane fait encore des ronds sur le trottoir. Papa ouvre la porte de la maison. Maman cherche un verre d'eau, pour la rose. Le livre, sur la table. Et la rose, dans le verre. Les deux métiers t'ont aidée. La libraire, puis la fleuriste. Le livre, et la vraie. Tu veux que je tourne une page ? Celle de la rose. La page et la tige se regardent, un peu. Une goutte glisse dans le verre, sans bruit. Merci d'avoir reculé le livre. Il est resté sec.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1776,7 +1826,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1848,10 +1898,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hortense serre la main de maman. Ils rentrent à la maison.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le platane fait encore des ronds sur le trottoir.
+narrateur|Papa ouvre la porte de la maison.
+narrateur|Maman cherche un verre d'eau, pour la rose.
+enfant-f|Le livre, sur la table.
+maman|Et la rose, dans le verre.
+papa|Les deux métiers t'ont aidée.
+papa|La libraire, puis la fleuriste.
+enfant-f|Le livre, et la vraie.
+maman|Tu veux que je tourne une page ?
+enfant-f|Celle de la rose.
+narrateur|La page et la tige se regardent, un peu.
+narrateur|Une goutte glisse dans le verre, sans bruit.
+papa|Merci d'avoir reculé le livre.
+maman|Il est resté sec.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1876,12 +1938,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La rose s'ouvre un peu, dans l'eau. La page reste plate, et sent encore la colle. J'ai les deux. Oui. Le quartier les a gardées pour toi. La clochette, tout au loin, ne tinte plus. Le verre chante une toute petite note, contre la table.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La rose s'ouvre un peu, dans l'eau. La page reste plate, et sent encore la colle. J'ai les deux. Oui. Le quartier les a gardées pour toi. La clochette, tout au loin, ne tinte plus. Le verre chante une toute petite note, contre la table.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1937,14 +1999,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2016,10 +2078,15 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La rose s'ouvre un peu, dans l'eau.
+narrateur|La page reste plate, et sent encore la colle.
+enfant-f|J'ai les deux.
+papa|Oui.
+maman|Le quartier les a gardées pour toi.
+narrateur|La clochette, tout au loin, ne tinte plus.
+narrateur|Le verre chante une toute petite note, contre la table.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2038,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2076,6 +2143,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.MET.001-07.xlsx
+++ b/stories/arbres/ATOM-SOC.MET.001-07.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>quartier, marché, cabinet, école</t>
+          <t>librairie du quartier, seau de la fleuriste, table de la maison</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hortense, maman, papa</t>
+          <t>Victorina, maman, papa</t>
         </is>
       </c>
     </row>
